--- a/founded bug/data/FMU.xlsx
+++ b/founded bug/data/FMU.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learning\matafeiyanll.github.io\founded bug\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowWidth="23040" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -879,19 +884,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -921,13 +920,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1488,19 +1480,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1509,127 +1510,118 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1640,61 +1632,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5286,7 +5278,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E3:E17 E19:E28 E30:E39 E41:E42 E63 E67:E79 E81 E88:E89 E92:E93 E95:E96 E99:E129" listDataValidation="1"/>
+    <ignoredError sqref="E99:E129 E95:E96 E92:E93 E88:E89 E81 E67:E79 E63 E41:E42 E30:E39 E19:E28 E3:E17" listDataValidation="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/founded bug/data/FMU.xlsx
+++ b/founded bug/data/FMU.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="279">
   <si>
     <t>Program</t>
   </si>
@@ -163,13 +163,10 @@
     <t>https://bugs.mysql.com/bug.php?id=120279</t>
   </si>
   <si>
-    <t>#120340</t>
-  </si>
-  <si>
-    <t>https://bugs.mysql.com/bug.php?id=120340</t>
-  </si>
-  <si>
-    <t>Not a bug</t>
+    <t>#121304</t>
+  </si>
+  <si>
+    <t>https://bugs.mysql.com/bug.php?id=121304</t>
   </si>
   <si>
     <t>#120359</t>
@@ -238,553 +235,553 @@
     <t>https://jira.mariadb.org/browse/MDEV-39354</t>
   </si>
   <si>
-    <t>MDEV-39434</t>
-  </si>
-  <si>
-    <t>https://jira.mariadb.org/browse/MDEV-39434</t>
+    <t>MDEV-41160</t>
+  </si>
+  <si>
+    <t>https://jira.mariadb.org/browse/MDEV-41160</t>
+  </si>
+  <si>
+    <t>Percona</t>
+  </si>
+  <si>
+    <t>PS-11042</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11042</t>
+  </si>
+  <si>
+    <t>PS-11043</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11043</t>
+  </si>
+  <si>
+    <t>PS-11044</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11044</t>
+  </si>
+  <si>
+    <t>PS-11045</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11045</t>
+  </si>
+  <si>
+    <t>PS-11046</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11046</t>
+  </si>
+  <si>
+    <t>PS-11047</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11047</t>
+  </si>
+  <si>
+    <t>PS-11048</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11048</t>
+  </si>
+  <si>
+    <t>PS-11049</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11049</t>
+  </si>
+  <si>
+    <t>PS-11050</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11050</t>
+  </si>
+  <si>
+    <t>PS-11051</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11051</t>
+  </si>
+  <si>
+    <t>PS-11055</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11055</t>
+  </si>
+  <si>
+    <t>PS-11102</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11102</t>
+  </si>
+  <si>
+    <t>PS-11103</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11103</t>
+  </si>
+  <si>
+    <t>PS-11105</t>
+  </si>
+  <si>
+    <t>https://perconadev.atlassian.net/browse/PS-11105</t>
+  </si>
+  <si>
+    <t>MonetDB</t>
+  </si>
+  <si>
+    <t>#7748</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7748</t>
+  </si>
+  <si>
+    <t>#7820</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7820</t>
+  </si>
+  <si>
+    <t>#7826</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7826</t>
+  </si>
+  <si>
+    <t>#7836</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7836</t>
+  </si>
+  <si>
+    <t>#7837</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7837</t>
+  </si>
+  <si>
+    <t>#7838</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7838</t>
+  </si>
+  <si>
+    <t>#7840</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7840</t>
+  </si>
+  <si>
+    <t>#7847</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7847</t>
+  </si>
+  <si>
+    <t>#7848</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7848</t>
+  </si>
+  <si>
+    <t>#7849</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7849</t>
+  </si>
+  <si>
+    <t>#7850</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7850</t>
+  </si>
+  <si>
+    <t>#7851</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7851</t>
+  </si>
+  <si>
+    <t>#7873</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7873</t>
+  </si>
+  <si>
+    <t>#7874</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7874</t>
+  </si>
+  <si>
+    <t>#7875</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7875</t>
+  </si>
+  <si>
+    <t>#7876</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7876</t>
+  </si>
+  <si>
+    <t>#7877</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7877</t>
+  </si>
+  <si>
+    <t>#7878</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7878</t>
+  </si>
+  <si>
+    <t>#7879</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7879</t>
+  </si>
+  <si>
+    <t>#7880</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7880</t>
+  </si>
+  <si>
+    <t>#7882</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7882</t>
+  </si>
+  <si>
+    <t>#7883</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7883</t>
+  </si>
+  <si>
+    <t>#7884</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7884</t>
+  </si>
+  <si>
+    <t>#7885</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7885</t>
+  </si>
+  <si>
+    <t>#7892</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7892</t>
+  </si>
+  <si>
+    <t>#7893</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7893</t>
+  </si>
+  <si>
+    <t>#7894</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7894</t>
+  </si>
+  <si>
+    <t>#7895</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7895</t>
+  </si>
+  <si>
+    <t>#7896</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7896</t>
+  </si>
+  <si>
+    <t>#7898</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7898</t>
+  </si>
+  <si>
+    <t>#7899</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7899</t>
+  </si>
+  <si>
+    <t>#7900</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7900</t>
+  </si>
+  <si>
+    <t>#7901</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7901</t>
+  </si>
+  <si>
+    <t>#7902</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7902</t>
+  </si>
+  <si>
+    <t>#7903</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7903</t>
+  </si>
+  <si>
+    <t>#7904</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7904</t>
+  </si>
+  <si>
+    <t>#7905</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7905</t>
+  </si>
+  <si>
+    <t>#7906</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7906</t>
+  </si>
+  <si>
+    <t>#7910</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7910</t>
+  </si>
+  <si>
+    <t>#7927</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7927</t>
+  </si>
+  <si>
+    <t>#7928</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7928</t>
+  </si>
+  <si>
+    <t>#7929</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7929</t>
+  </si>
+  <si>
+    <t>#7930</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7930</t>
+  </si>
+  <si>
+    <t>#7931</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7931</t>
+  </si>
+  <si>
+    <t>#7932</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7932</t>
+  </si>
+  <si>
+    <t>#7933</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7933</t>
+  </si>
+  <si>
+    <t>#7934</t>
+  </si>
+  <si>
+    <t>https://github.com/MonetDB/MonetDB/issues/7934</t>
+  </si>
+  <si>
+    <t>TiDB</t>
+  </si>
+  <si>
+    <t>#67650</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/67650</t>
+  </si>
+  <si>
+    <t>#67781</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/67781</t>
+  </si>
+  <si>
+    <t>#68031</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/68031</t>
+  </si>
+  <si>
+    <t>#68098</t>
+  </si>
+  <si>
+    <t>https://github.com/pingcap/tidb/issues/68098</t>
+  </si>
+  <si>
+    <t>DuckDB</t>
+  </si>
+  <si>
+    <t>#19355</t>
+  </si>
+  <si>
+    <t>https://github.com/duckdb/duckdb/issues/19355</t>
+  </si>
+  <si>
+    <t>#22025</t>
+  </si>
+  <si>
+    <t>https://github.com/duckdb/duckdb/issues/22025</t>
+  </si>
+  <si>
+    <t>#22267</t>
+  </si>
+  <si>
+    <t>https://github.com/duckdb/duckdb/issues/22267</t>
+  </si>
+  <si>
+    <t>PolarDB</t>
+  </si>
+  <si>
+    <t>#270</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/270</t>
+  </si>
+  <si>
+    <t>#274</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/274</t>
+  </si>
+  <si>
+    <t>#271</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/271</t>
+  </si>
+  <si>
+    <t>#272</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/272</t>
+  </si>
+  <si>
+    <t>#273</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/273</t>
+  </si>
+  <si>
+    <t>#275</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/275</t>
+  </si>
+  <si>
+    <t>#276</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/276</t>
+  </si>
+  <si>
+    <t>#277</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/277</t>
+  </si>
+  <si>
+    <t>#278</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/278</t>
+  </si>
+  <si>
+    <t>#279</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/279</t>
+  </si>
+  <si>
+    <t>#280</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/280</t>
+  </si>
+  <si>
+    <t>#281</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/281</t>
+  </si>
+  <si>
+    <t>#282</t>
+  </si>
+  <si>
+    <t>https://github.com/polardb/polardbx-sql/issues/282</t>
+  </si>
+  <si>
+    <t>ClickHouse</t>
+  </si>
+  <si>
+    <t>#105760</t>
+  </si>
+  <si>
+    <t>https://github.com/ClickHouse/ClickHouse/issues/105760</t>
+  </si>
+  <si>
+    <t>#105815</t>
+  </si>
+  <si>
+    <t>https://github.com/ClickHouse/ClickHouse/issues/105815</t>
+  </si>
+  <si>
+    <t>#105817</t>
+  </si>
+  <si>
+    <t>https://github.com/ClickHouse/ClickHouse/issues/105817</t>
+  </si>
+  <si>
+    <t>#105824</t>
+  </si>
+  <si>
+    <t>https://github.com/ClickHouse/ClickHouse/issues/105824</t>
+  </si>
+  <si>
+    <t>#105825</t>
+  </si>
+  <si>
+    <t>https://github.com/ClickHouse/ClickHouse/issues/105825</t>
+  </si>
+  <si>
+    <t>#105826</t>
+  </si>
+  <si>
+    <t>https://github.com/ClickHouse/ClickHouse/issues/105826</t>
   </si>
   <si>
     <t>Waiting</t>
-  </si>
-  <si>
-    <t>Percona</t>
-  </si>
-  <si>
-    <t>PS-11042</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11042</t>
-  </si>
-  <si>
-    <t>PS-11043</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11043</t>
-  </si>
-  <si>
-    <t>PS-11044</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11044</t>
-  </si>
-  <si>
-    <t>PS-11045</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11045</t>
-  </si>
-  <si>
-    <t>PS-11046</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11046</t>
-  </si>
-  <si>
-    <t>PS-11047</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11047</t>
-  </si>
-  <si>
-    <t>PS-11048</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11048</t>
-  </si>
-  <si>
-    <t>PS-11049</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11049</t>
-  </si>
-  <si>
-    <t>PS-11050</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11050</t>
-  </si>
-  <si>
-    <t>PS-11051</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11051</t>
-  </si>
-  <si>
-    <t>PS-11055</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11055</t>
-  </si>
-  <si>
-    <t>PS-11102</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11102</t>
-  </si>
-  <si>
-    <t>PS-11103</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11103</t>
-  </si>
-  <si>
-    <t>PS-11105</t>
-  </si>
-  <si>
-    <t>https://perconadev.atlassian.net/browse/PS-11105</t>
-  </si>
-  <si>
-    <t>MonetDB</t>
-  </si>
-  <si>
-    <t>#7748</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7748</t>
-  </si>
-  <si>
-    <t>#7820</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7820</t>
-  </si>
-  <si>
-    <t>#7826</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7826</t>
-  </si>
-  <si>
-    <t>#7836</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7836</t>
-  </si>
-  <si>
-    <t>#7837</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7837</t>
-  </si>
-  <si>
-    <t>#7838</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7838</t>
-  </si>
-  <si>
-    <t>#7840</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7840</t>
-  </si>
-  <si>
-    <t>#7847</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7847</t>
-  </si>
-  <si>
-    <t>#7848</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7848</t>
-  </si>
-  <si>
-    <t>#7849</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7849</t>
-  </si>
-  <si>
-    <t>#7850</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7850</t>
-  </si>
-  <si>
-    <t>#7851</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7851</t>
-  </si>
-  <si>
-    <t>#7873</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7873</t>
-  </si>
-  <si>
-    <t>#7874</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7874</t>
-  </si>
-  <si>
-    <t>#7875</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7875</t>
-  </si>
-  <si>
-    <t>#7876</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7876</t>
-  </si>
-  <si>
-    <t>#7877</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7877</t>
-  </si>
-  <si>
-    <t>#7878</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7878</t>
-  </si>
-  <si>
-    <t>#7879</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7879</t>
-  </si>
-  <si>
-    <t>#7880</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7880</t>
-  </si>
-  <si>
-    <t>#7882</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7882</t>
-  </si>
-  <si>
-    <t>#7883</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7883</t>
-  </si>
-  <si>
-    <t>#7884</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7884</t>
-  </si>
-  <si>
-    <t>#7885</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7885</t>
-  </si>
-  <si>
-    <t>#7892</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7892</t>
-  </si>
-  <si>
-    <t>#7893</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7893</t>
-  </si>
-  <si>
-    <t>#7894</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7894</t>
-  </si>
-  <si>
-    <t>#7895</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7895</t>
-  </si>
-  <si>
-    <t>#7896</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7896</t>
-  </si>
-  <si>
-    <t>#7898</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7898</t>
-  </si>
-  <si>
-    <t>#7899</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7899</t>
-  </si>
-  <si>
-    <t>#7900</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7900</t>
-  </si>
-  <si>
-    <t>#7901</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7901</t>
-  </si>
-  <si>
-    <t>#7902</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7902</t>
-  </si>
-  <si>
-    <t>#7903</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7903</t>
-  </si>
-  <si>
-    <t>#7904</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7904</t>
-  </si>
-  <si>
-    <t>#7905</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7905</t>
-  </si>
-  <si>
-    <t>#7906</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7906</t>
-  </si>
-  <si>
-    <t>#7910</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7910</t>
-  </si>
-  <si>
-    <t>#7927</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7927</t>
-  </si>
-  <si>
-    <t>#7928</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7928</t>
-  </si>
-  <si>
-    <t>#7929</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7929</t>
-  </si>
-  <si>
-    <t>#7930</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7930</t>
-  </si>
-  <si>
-    <t>#7931</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7931</t>
-  </si>
-  <si>
-    <t>#7932</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7932</t>
-  </si>
-  <si>
-    <t>#7933</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7933</t>
-  </si>
-  <si>
-    <t>#7934</t>
-  </si>
-  <si>
-    <t>https://github.com/MonetDB/MonetDB/issues/7934</t>
-  </si>
-  <si>
-    <t>TiDB</t>
-  </si>
-  <si>
-    <t>#67650</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/67650</t>
-  </si>
-  <si>
-    <t>#67781</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/67781</t>
-  </si>
-  <si>
-    <t>#68031</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/68031</t>
-  </si>
-  <si>
-    <t>#68098</t>
-  </si>
-  <si>
-    <t>https://github.com/pingcap/tidb/issues/68098</t>
-  </si>
-  <si>
-    <t>DuckDB</t>
-  </si>
-  <si>
-    <t>#19355</t>
-  </si>
-  <si>
-    <t>https://github.com/duckdb/duckdb/issues/19355</t>
-  </si>
-  <si>
-    <t>#22025</t>
-  </si>
-  <si>
-    <t>https://github.com/duckdb/duckdb/issues/22025</t>
-  </si>
-  <si>
-    <t>#22267</t>
-  </si>
-  <si>
-    <t>https://github.com/duckdb/duckdb/issues/22267</t>
-  </si>
-  <si>
-    <t>PolarDB</t>
-  </si>
-  <si>
-    <t>#270</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/270</t>
-  </si>
-  <si>
-    <t>#274</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/274</t>
-  </si>
-  <si>
-    <t>#271</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/271</t>
-  </si>
-  <si>
-    <t>#272</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/272</t>
-  </si>
-  <si>
-    <t>#273</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/273</t>
-  </si>
-  <si>
-    <t>#275</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/275</t>
-  </si>
-  <si>
-    <t>#276</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/276</t>
-  </si>
-  <si>
-    <t>#277</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/277</t>
-  </si>
-  <si>
-    <t>#278</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/278</t>
-  </si>
-  <si>
-    <t>#279</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/279</t>
-  </si>
-  <si>
-    <t>#280</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/280</t>
-  </si>
-  <si>
-    <t>#281</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/281</t>
-  </si>
-  <si>
-    <t>#282</t>
-  </si>
-  <si>
-    <t>https://github.com/polardb/polardbx-sql/issues/282</t>
-  </si>
-  <si>
-    <t>ClickHouse</t>
-  </si>
-  <si>
-    <t>#105760</t>
-  </si>
-  <si>
-    <t>https://github.com/ClickHouse/ClickHouse/issues/105760</t>
-  </si>
-  <si>
-    <t>#105815</t>
-  </si>
-  <si>
-    <t>https://github.com/ClickHouse/ClickHouse/issues/105815</t>
-  </si>
-  <si>
-    <t>#105817</t>
-  </si>
-  <si>
-    <t>https://github.com/ClickHouse/ClickHouse/issues/105817</t>
-  </si>
-  <si>
-    <t>#105824</t>
-  </si>
-  <si>
-    <t>https://github.com/ClickHouse/ClickHouse/issues/105824</t>
-  </si>
-  <si>
-    <t>#105825</t>
-  </si>
-  <si>
-    <t>https://github.com/ClickHouse/ClickHouse/issues/105825</t>
-  </si>
-  <si>
-    <t>#105826</t>
-  </si>
-  <si>
-    <t>https://github.com/ClickHouse/ClickHouse/issues/105826</t>
   </si>
   <si>
     <t>#105827</t>
@@ -2554,7 +2551,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>12</v>
@@ -2568,10 +2565,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>10</v>
@@ -2591,10 +2588,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>15</v>
@@ -2614,10 +2611,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>15</v>
@@ -2637,10 +2634,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>15</v>
@@ -2654,22 +2651,22 @@
     </row>
     <row r="22" ht="15.35" spans="1:7">
       <c r="A22" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="12">
         <v>21</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="E22" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>12</v>
@@ -2677,16 +2674,16 @@
     </row>
     <row r="23" ht="15.35" spans="1:7">
       <c r="A23" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="12">
         <v>22</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>15</v>
@@ -2700,16 +2697,16 @@
     </row>
     <row r="24" ht="15.35" spans="1:7">
       <c r="A24" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" s="12">
         <v>23</v>
       </c>
       <c r="C24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>61</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>15</v>
@@ -2723,16 +2720,16 @@
     </row>
     <row r="25" ht="15.35" spans="1:7">
       <c r="A25" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="12">
         <v>24</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>15</v>
@@ -2746,22 +2743,22 @@
     </row>
     <row r="26" ht="15.35" spans="1:7">
       <c r="A26" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="12">
         <v>25</v>
       </c>
       <c r="C26" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E26" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>12</v>
@@ -2769,16 +2766,16 @@
     </row>
     <row r="27" ht="15.35" spans="1:7">
       <c r="A27" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" s="12">
         <v>26</v>
       </c>
       <c r="C27" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>15</v>
@@ -2792,22 +2789,22 @@
     </row>
     <row r="28" ht="15.35" spans="1:7">
       <c r="A28" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" s="12">
         <v>27</v>
       </c>
       <c r="C28" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="E28" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>12</v>
@@ -2815,16 +2812,16 @@
     </row>
     <row r="29" ht="15.35" spans="1:7">
       <c r="A29" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B29" s="12">
         <v>28</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>10</v>
@@ -2838,16 +2835,16 @@
     </row>
     <row r="30" ht="15.35" spans="1:7">
       <c r="A30" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B30" s="12">
         <v>29</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>15</v>
@@ -2861,16 +2858,16 @@
     </row>
     <row r="31" ht="15.35" spans="1:7">
       <c r="A31" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="12">
         <v>30</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>15</v>
@@ -2884,16 +2881,16 @@
     </row>
     <row r="32" ht="15.35" spans="1:7">
       <c r="A32" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B32" s="12">
         <v>31</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>15</v>
@@ -2907,16 +2904,16 @@
     </row>
     <row r="33" ht="15.35" spans="1:7">
       <c r="A33" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B33" s="12">
         <v>32</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>15</v>
@@ -2930,16 +2927,16 @@
     </row>
     <row r="34" ht="15.35" spans="1:7">
       <c r="A34" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B34" s="12">
         <v>33</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>15</v>
@@ -2953,16 +2950,16 @@
     </row>
     <row r="35" ht="15.35" spans="1:7">
       <c r="A35" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B35" s="12">
         <v>34</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>15</v>
@@ -2976,16 +2973,16 @@
     </row>
     <row r="36" ht="15.35" spans="1:7">
       <c r="A36" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B36" s="12">
         <v>35</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>15</v>
@@ -2999,16 +2996,16 @@
     </row>
     <row r="37" ht="15.35" spans="1:7">
       <c r="A37" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" s="12">
         <v>36</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>15</v>
@@ -3022,16 +3019,16 @@
     </row>
     <row r="38" ht="15.35" spans="1:7">
       <c r="A38" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B38" s="12">
         <v>37</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>15</v>
@@ -3045,16 +3042,16 @@
     </row>
     <row r="39" ht="15.35" spans="1:7">
       <c r="A39" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B39" s="12">
         <v>38</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>15</v>
@@ -3068,16 +3065,16 @@
     </row>
     <row r="40" ht="15.35" spans="1:7">
       <c r="A40" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B40" s="12">
         <v>39</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E40" s="13" t="s">
         <v>10</v>
@@ -3091,16 +3088,16 @@
     </row>
     <row r="41" ht="15.35" spans="1:7">
       <c r="A41" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B41" s="12">
         <v>40</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>15</v>
@@ -3114,16 +3111,16 @@
     </row>
     <row r="42" ht="15.35" spans="1:7">
       <c r="A42" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B42" s="12">
         <v>41</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E42" s="13" t="s">
         <v>15</v>
@@ -3137,22 +3134,22 @@
     </row>
     <row r="43" ht="15.35" spans="1:7">
       <c r="A43" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B43" s="12">
         <v>42</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43" s="15" t="s">
         <v>12</v>
@@ -3160,22 +3157,22 @@
     </row>
     <row r="44" ht="15.35" spans="1:7">
       <c r="A44" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B44" s="12">
         <v>43</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G44" s="15" t="s">
         <v>12</v>
@@ -3183,22 +3180,22 @@
     </row>
     <row r="45" ht="15.35" spans="1:7">
       <c r="A45" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B45" s="12">
         <v>44</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45" s="15" t="s">
         <v>12</v>
@@ -3206,22 +3203,22 @@
     </row>
     <row r="46" ht="15.35" spans="1:7">
       <c r="A46" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B46" s="12">
         <v>45</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G46" s="15" t="s">
         <v>12</v>
@@ -3229,22 +3226,22 @@
     </row>
     <row r="47" ht="15.35" spans="1:7">
       <c r="A47" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B47" s="12">
         <v>46</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G47" s="15" t="s">
         <v>12</v>
@@ -3252,22 +3249,22 @@
     </row>
     <row r="48" ht="15.35" spans="1:7">
       <c r="A48" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B48" s="12">
         <v>47</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E48" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G48" s="15" t="s">
         <v>12</v>
@@ -3275,22 +3272,22 @@
     </row>
     <row r="49" ht="15.35" spans="1:7">
       <c r="A49" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B49" s="12">
         <v>48</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G49" s="15" t="s">
         <v>12</v>
@@ -3298,22 +3295,22 @@
     </row>
     <row r="50" ht="15.35" spans="1:7">
       <c r="A50" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B50" s="12">
         <v>49</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G50" s="15" t="s">
         <v>12</v>
@@ -3321,22 +3318,22 @@
     </row>
     <row r="51" ht="15.35" spans="1:7">
       <c r="A51" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B51" s="12">
         <v>50</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E51" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G51" s="15" t="s">
         <v>12</v>
@@ -3344,22 +3341,22 @@
     </row>
     <row r="52" ht="15.35" spans="1:7">
       <c r="A52" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B52" s="12">
         <v>51</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G52" s="15" t="s">
         <v>12</v>
@@ -3367,22 +3364,22 @@
     </row>
     <row r="53" ht="15.35" spans="1:7">
       <c r="A53" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B53" s="12">
         <v>52</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E53" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G53" s="15" t="s">
         <v>12</v>
@@ -3390,22 +3387,22 @@
     </row>
     <row r="54" ht="15.35" spans="1:7">
       <c r="A54" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B54" s="12">
         <v>53</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G54" s="15" t="s">
         <v>12</v>
@@ -3413,22 +3410,22 @@
     </row>
     <row r="55" ht="15.35" spans="1:7">
       <c r="A55" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B55" s="12">
         <v>54</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E55" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G55" s="15" t="s">
         <v>12</v>
@@ -3436,22 +3433,22 @@
     </row>
     <row r="56" ht="15.35" spans="1:7">
       <c r="A56" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B56" s="12">
         <v>55</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G56" s="15" t="s">
         <v>12</v>
@@ -3459,22 +3456,22 @@
     </row>
     <row r="57" ht="15.35" spans="1:7">
       <c r="A57" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B57" s="12">
         <v>56</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G57" s="15" t="s">
         <v>12</v>
@@ -3482,22 +3479,22 @@
     </row>
     <row r="58" ht="15.35" spans="1:7">
       <c r="A58" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B58" s="12">
         <v>57</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G58" s="15" t="s">
         <v>12</v>
@@ -3505,22 +3502,22 @@
     </row>
     <row r="59" ht="15.35" spans="1:7">
       <c r="A59" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B59" s="12">
         <v>58</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G59" s="15" t="s">
         <v>12</v>
@@ -3528,22 +3525,22 @@
     </row>
     <row r="60" ht="15.35" spans="1:7">
       <c r="A60" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B60" s="12">
         <v>59</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G60" s="15" t="s">
         <v>12</v>
@@ -3551,22 +3548,22 @@
     </row>
     <row r="61" ht="15.35" spans="1:7">
       <c r="A61" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B61" s="12">
         <v>60</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G61" s="15" t="s">
         <v>12</v>
@@ -3574,22 +3571,22 @@
     </row>
     <row r="62" ht="15.35" spans="1:7">
       <c r="A62" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B62" s="12">
         <v>61</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G62" s="15" t="s">
         <v>12</v>
@@ -3597,22 +3594,22 @@
     </row>
     <row r="63" ht="15.35" spans="1:7">
       <c r="A63" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B63" s="12">
         <v>62</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E63" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G63" s="15" t="s">
         <v>12</v>
@@ -3620,22 +3617,22 @@
     </row>
     <row r="64" ht="15.35" spans="1:7">
       <c r="A64" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B64" s="12">
         <v>63</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G64" s="15" t="s">
         <v>12</v>
@@ -3643,22 +3640,22 @@
     </row>
     <row r="65" ht="15.35" spans="1:7">
       <c r="A65" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B65" s="12">
         <v>64</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E65" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>12</v>
@@ -3666,22 +3663,22 @@
     </row>
     <row r="66" ht="15.35" spans="1:7">
       <c r="A66" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B66" s="12">
         <v>65</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>12</v>
@@ -3689,22 +3686,22 @@
     </row>
     <row r="67" ht="15.35" spans="1:7">
       <c r="A67" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B67" s="12">
         <v>66</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>12</v>
@@ -3712,22 +3709,22 @@
     </row>
     <row r="68" ht="15.35" spans="1:7">
       <c r="A68" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B68" s="12">
         <v>67</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E68" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G68" s="20" t="s">
         <v>12</v>
@@ -3735,22 +3732,22 @@
     </row>
     <row r="69" ht="15.35" spans="1:7">
       <c r="A69" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B69" s="12">
         <v>68</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G69" s="20" t="s">
         <v>12</v>
@@ -3758,22 +3755,22 @@
     </row>
     <row r="70" ht="15.35" spans="1:7">
       <c r="A70" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B70" s="12">
         <v>69</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E70" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G70" s="20" t="s">
         <v>12</v>
@@ -3781,22 +3778,22 @@
     </row>
     <row r="71" ht="15.35" spans="1:7">
       <c r="A71" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B71" s="12">
         <v>70</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E71" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G71" s="20" t="s">
         <v>12</v>
@@ -3804,22 +3801,22 @@
     </row>
     <row r="72" ht="15.35" spans="1:7">
       <c r="A72" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B72" s="12">
         <v>71</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G72" s="20" t="s">
         <v>12</v>
@@ -3827,22 +3824,22 @@
     </row>
     <row r="73" ht="15.35" spans="1:7">
       <c r="A73" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B73" s="12">
         <v>72</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E73" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>12</v>
@@ -3850,22 +3847,22 @@
     </row>
     <row r="74" ht="15.35" spans="1:7">
       <c r="A74" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B74" s="12">
         <v>73</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E74" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G74" s="20" t="s">
         <v>12</v>
@@ -3873,22 +3870,22 @@
     </row>
     <row r="75" ht="15.35" spans="1:7">
       <c r="A75" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B75" s="12">
         <v>74</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E75" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G75" s="20" t="s">
         <v>12</v>
@@ -3896,22 +3893,22 @@
     </row>
     <row r="76" ht="15.35" spans="1:7">
       <c r="A76" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B76" s="12">
         <v>75</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G76" s="20" t="s">
         <v>12</v>
@@ -3919,22 +3916,22 @@
     </row>
     <row r="77" ht="15.35" spans="1:7">
       <c r="A77" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B77" s="12">
         <v>76</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G77" s="20" t="s">
         <v>12</v>
@@ -3942,22 +3939,22 @@
     </row>
     <row r="78" ht="15.35" spans="1:7">
       <c r="A78" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B78" s="12">
         <v>77</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G78" s="20" t="s">
         <v>12</v>
@@ -3965,22 +3962,22 @@
     </row>
     <row r="79" ht="15.35" spans="1:7">
       <c r="A79" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B79" s="12">
         <v>78</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F79" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>12</v>
@@ -3988,22 +3985,22 @@
     </row>
     <row r="80" ht="15.35" spans="1:7">
       <c r="A80" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B80" s="12">
         <v>79</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G80" s="20" t="s">
         <v>12</v>
@@ -4011,22 +4008,22 @@
     </row>
     <row r="81" ht="15.35" spans="1:7">
       <c r="A81" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B81" s="12">
         <v>80</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E81" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F81" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G81" s="20" t="s">
         <v>12</v>
@@ -4034,22 +4031,22 @@
     </row>
     <row r="82" ht="15.35" spans="1:7">
       <c r="A82" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B82" s="12">
         <v>81</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G82" s="20" t="s">
         <v>12</v>
@@ -4057,22 +4054,22 @@
     </row>
     <row r="83" ht="15.35" spans="1:7">
       <c r="A83" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B83" s="12">
         <v>82</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G83" s="20" t="s">
         <v>12</v>
@@ -4080,22 +4077,22 @@
     </row>
     <row r="84" ht="15.35" spans="1:7">
       <c r="A84" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B84" s="12">
         <v>83</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F84" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G84" s="20" t="s">
         <v>12</v>
@@ -4103,22 +4100,22 @@
     </row>
     <row r="85" ht="15.35" spans="1:7">
       <c r="A85" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B85" s="12">
         <v>84</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G85" s="20" t="s">
         <v>12</v>
@@ -4126,22 +4123,22 @@
     </row>
     <row r="86" ht="15.35" spans="1:7">
       <c r="A86" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B86" s="12">
         <v>85</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E86" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G86" s="20" t="s">
         <v>12</v>
@@ -4149,22 +4146,22 @@
     </row>
     <row r="87" ht="15.35" spans="1:7">
       <c r="A87" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B87" s="12">
         <v>86</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E87" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G87" s="20" t="s">
         <v>12</v>
@@ -4172,22 +4169,22 @@
     </row>
     <row r="88" ht="15.35" spans="1:7">
       <c r="A88" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B88" s="12">
         <v>87</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E88" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G88" s="20" t="s">
         <v>12</v>
@@ -4195,22 +4192,22 @@
     </row>
     <row r="89" ht="15.35" spans="1:7">
       <c r="A89" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B89" s="12">
         <v>88</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E89" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G89" s="20" t="s">
         <v>12</v>
@@ -4218,16 +4215,16 @@
     </row>
     <row r="90" ht="15.35" spans="1:7">
       <c r="A90" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B90" s="12">
         <v>89</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="13" t="s">
         <v>10</v>
@@ -4241,16 +4238,16 @@
     </row>
     <row r="91" ht="15.35" spans="1:7">
       <c r="A91" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B91" s="12">
         <v>90</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>10</v>
@@ -4264,16 +4261,16 @@
     </row>
     <row r="92" ht="15.35" spans="1:7">
       <c r="A92" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B92" s="12">
         <v>91</v>
       </c>
       <c r="C92" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E92" s="13" t="s">
         <v>15</v>
@@ -4287,16 +4284,16 @@
     </row>
     <row r="93" ht="15.35" spans="1:7">
       <c r="A93" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B93" s="12">
         <v>92</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E93" s="13" t="s">
         <v>15</v>
@@ -4310,22 +4307,22 @@
     </row>
     <row r="94" ht="15.35" spans="1:7">
       <c r="A94" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B94" s="12">
         <v>93</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="13" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G94" s="20" t="s">
         <v>12</v>
@@ -4333,16 +4330,16 @@
     </row>
     <row r="95" ht="15.35" spans="1:7">
       <c r="A95" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B95" s="12">
         <v>94</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="13" t="s">
         <v>15</v>
@@ -4356,22 +4353,22 @@
     </row>
     <row r="96" ht="15.35" spans="1:7">
       <c r="A96" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B96" s="12">
         <v>95</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G96" s="20" t="s">
         <v>12</v>
@@ -4379,16 +4376,16 @@
     </row>
     <row r="97" ht="15.35" spans="1:7">
       <c r="A97" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B97" s="12">
         <v>96</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E97" s="13" t="s">
         <v>10</v>
@@ -4402,16 +4399,16 @@
     </row>
     <row r="98" ht="15.35" spans="1:7">
       <c r="A98" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B98" s="12">
         <v>97</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E98" s="13" t="s">
         <v>10</v>
@@ -4425,16 +4422,16 @@
     </row>
     <row r="99" ht="15.35" spans="1:7">
       <c r="A99" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B99" s="12">
         <v>98</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E99" s="13" t="s">
         <v>15</v>
@@ -4448,16 +4445,16 @@
     </row>
     <row r="100" ht="15.35" spans="1:7">
       <c r="A100" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B100" s="12">
         <v>99</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E100" s="13" t="s">
         <v>15</v>
@@ -4471,16 +4468,16 @@
     </row>
     <row r="101" ht="15.35" spans="1:7">
       <c r="A101" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B101" s="12">
         <v>100</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E101" s="13" t="s">
         <v>15</v>
@@ -4494,16 +4491,16 @@
     </row>
     <row r="102" ht="15.35" spans="1:7">
       <c r="A102" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B102" s="12">
         <v>101</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E102" s="13" t="s">
         <v>15</v>
@@ -4517,16 +4514,16 @@
     </row>
     <row r="103" ht="15.35" spans="1:7">
       <c r="A103" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B103" s="12">
         <v>102</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E103" s="13" t="s">
         <v>15</v>
@@ -4540,16 +4537,16 @@
     </row>
     <row r="104" ht="15.35" spans="1:7">
       <c r="A104" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B104" s="12">
         <v>103</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>15</v>
@@ -4563,16 +4560,16 @@
     </row>
     <row r="105" ht="15.35" spans="1:7">
       <c r="A105" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B105" s="12">
         <v>104</v>
       </c>
       <c r="C105" s="20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>15</v>
@@ -4586,16 +4583,16 @@
     </row>
     <row r="106" ht="15.35" spans="1:7">
       <c r="A106" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B106" s="12">
         <v>105</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E106" s="13" t="s">
         <v>15</v>
@@ -4609,16 +4606,16 @@
     </row>
     <row r="107" ht="15.35" spans="1:7">
       <c r="A107" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B107" s="12">
         <v>106</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E107" s="13" t="s">
         <v>15</v>
@@ -4632,16 +4629,16 @@
     </row>
     <row r="108" ht="15.35" spans="1:7">
       <c r="A108" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B108" s="12">
         <v>107</v>
       </c>
       <c r="C108" s="20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>15</v>
@@ -4655,16 +4652,16 @@
     </row>
     <row r="109" ht="15.35" spans="1:7">
       <c r="A109" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B109" s="12">
         <v>108</v>
       </c>
       <c r="C109" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E109" s="13" t="s">
         <v>15</v>
@@ -4678,22 +4675,22 @@
     </row>
     <row r="110" ht="15.35" spans="1:7">
       <c r="A110" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B110" s="12">
         <v>109</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F110" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G110" s="20" t="s">
         <v>12</v>
@@ -4701,22 +4698,22 @@
     </row>
     <row r="111" ht="15.35" spans="1:7">
       <c r="A111" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B111" s="12">
         <v>110</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E111" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G111" s="20" t="s">
         <v>12</v>
@@ -4724,16 +4721,16 @@
     </row>
     <row r="112" ht="15.35" spans="1:7">
       <c r="A112" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B112" s="12">
         <v>111</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>15</v>
@@ -4747,16 +4744,16 @@
     </row>
     <row r="113" ht="15.35" spans="1:7">
       <c r="A113" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B113" s="12">
         <v>112</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E113" s="13" t="s">
         <v>15</v>
@@ -4770,16 +4767,16 @@
     </row>
     <row r="114" ht="15.35" spans="1:7">
       <c r="A114" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B114" s="12">
         <v>113</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>15</v>
@@ -4793,22 +4790,22 @@
     </row>
     <row r="115" ht="15.35" spans="1:7">
       <c r="A115" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B115" s="12">
         <v>114</v>
       </c>
       <c r="C115" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" s="20" t="s">
         <v>249</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F115" s="20" t="s">
-        <v>70</v>
       </c>
       <c r="G115" s="20" t="s">
         <v>12</v>
@@ -4816,22 +4813,22 @@
     </row>
     <row r="116" ht="15.35" spans="1:7">
       <c r="A116" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B116" s="12">
         <v>115</v>
       </c>
       <c r="C116" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D116" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="D116" s="9" t="s">
-        <v>252</v>
-      </c>
       <c r="E116" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F116" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G116" s="20" t="s">
         <v>12</v>
@@ -4839,22 +4836,22 @@
     </row>
     <row r="117" ht="15.35" spans="1:7">
       <c r="A117" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B117" s="12">
         <v>116</v>
       </c>
       <c r="C117" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="D117" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="D117" s="9" t="s">
-        <v>255</v>
-      </c>
       <c r="E117" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G117" s="20" t="s">
         <v>12</v>
@@ -4862,22 +4859,22 @@
     </row>
     <row r="118" ht="15.35" spans="1:7">
       <c r="A118" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B118" s="12">
         <v>117</v>
       </c>
       <c r="C118" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D118" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="D118" s="9" t="s">
-        <v>257</v>
-      </c>
       <c r="E118" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F118" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G118" s="20" t="s">
         <v>12</v>
@@ -4885,22 +4882,22 @@
     </row>
     <row r="119" ht="15.35" spans="1:7">
       <c r="A119" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B119" s="12">
         <v>118</v>
       </c>
       <c r="C119" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="D119" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="D119" s="9" t="s">
-        <v>259</v>
-      </c>
       <c r="E119" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G119" s="20" t="s">
         <v>12</v>
@@ -4908,22 +4905,22 @@
     </row>
     <row r="120" ht="15.35" spans="1:7">
       <c r="A120" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B120" s="12">
         <v>119</v>
       </c>
       <c r="C120" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D120" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="D120" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="E120" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F120" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G120" s="20" t="s">
         <v>12</v>
@@ -4931,22 +4928,22 @@
     </row>
     <row r="121" ht="15.35" spans="1:7">
       <c r="A121" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B121" s="12">
         <v>120</v>
       </c>
       <c r="C121" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="D121" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="D121" s="9" t="s">
-        <v>263</v>
-      </c>
       <c r="E121" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G121" s="20" t="s">
         <v>12</v>
@@ -4954,22 +4951,22 @@
     </row>
     <row r="122" ht="15.35" spans="1:7">
       <c r="A122" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B122" s="12">
         <v>121</v>
       </c>
       <c r="C122" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D122" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="D122" s="9" t="s">
-        <v>265</v>
-      </c>
       <c r="E122" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G122" s="20" t="s">
         <v>12</v>
@@ -4977,22 +4974,22 @@
     </row>
     <row r="123" ht="15.35" spans="1:7">
       <c r="A123" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B123" s="12">
         <v>122</v>
       </c>
       <c r="C123" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D123" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="D123" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="E123" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G123" s="20" t="s">
         <v>12</v>
@@ -5000,22 +4997,22 @@
     </row>
     <row r="124" ht="15.35" spans="1:7">
       <c r="A124" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B124" s="12">
         <v>123</v>
       </c>
       <c r="C124" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D124" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="D124" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="E124" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F124" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G124" s="20" t="s">
         <v>12</v>
@@ -5023,22 +5020,22 @@
     </row>
     <row r="125" ht="15.35" spans="1:7">
       <c r="A125" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B125" s="12">
         <v>124</v>
       </c>
       <c r="C125" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="D125" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="D125" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="E125" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F125" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G125" s="20" t="s">
         <v>12</v>
@@ -5046,22 +5043,22 @@
     </row>
     <row r="126" ht="15.35" spans="1:7">
       <c r="A126" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B126" s="12">
         <v>125</v>
       </c>
       <c r="C126" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="D126" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>273</v>
-      </c>
       <c r="E126" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F126" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G126" s="20" t="s">
         <v>12</v>
@@ -5069,22 +5066,22 @@
     </row>
     <row r="127" ht="15.35" spans="1:7">
       <c r="A127" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B127" s="12">
         <v>126</v>
       </c>
       <c r="C127" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="D127" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="D127" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="E127" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F127" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G127" s="20" t="s">
         <v>12</v>
@@ -5092,22 +5089,22 @@
     </row>
     <row r="128" ht="15.35" spans="1:7">
       <c r="A128" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B128" s="12">
         <v>127</v>
       </c>
       <c r="C128" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="D128" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="D128" s="9" t="s">
-        <v>277</v>
-      </c>
       <c r="E128" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F128" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G128" s="20" t="s">
         <v>12</v>
@@ -5115,22 +5112,22 @@
     </row>
     <row r="129" ht="15.35" spans="1:7">
       <c r="A129" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B129" s="12">
         <v>128</v>
       </c>
       <c r="C129" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="D129" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="D129" s="9" t="s">
-        <v>279</v>
-      </c>
       <c r="E129" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G129" s="20" t="s">
         <v>12</v>
@@ -5160,7 +5157,7 @@
     <hyperlink ref="D14" r:id="rId13" display="https://bugs.mysql.com/bug.php?id=120225"/>
     <hyperlink ref="D15" r:id="rId14" display="https://bugs.mysql.com/bug.php?id=120271"/>
     <hyperlink ref="D16" r:id="rId15" display="https://bugs.mysql.com/bug.php?id=120279"/>
-    <hyperlink ref="D17" r:id="rId16" display="https://bugs.mysql.com/bug.php?id=120340"/>
+    <hyperlink ref="D17" r:id="rId16" display="https://bugs.mysql.com/bug.php?id=121304" tooltip="https://bugs.mysql.com/bug.php?id=121304"/>
     <hyperlink ref="D18" r:id="rId17" display="https://bugs.mysql.com/bug.php?id=120359"/>
     <hyperlink ref="D19" r:id="rId18" display="https://bugs.mysql.com/bug.php?id=120363"/>
     <hyperlink ref="D20" r:id="rId19" display="https://bugs.mysql.com/bug.php?id=120377"/>
@@ -5171,7 +5168,7 @@
     <hyperlink ref="D25" r:id="rId24" display="https://jira.mariadb.org/browse/MDEV-39238"/>
     <hyperlink ref="D26" r:id="rId25" display="https://jira.mariadb.org/browse/MDEV-39284"/>
     <hyperlink ref="D27" r:id="rId26" display="https://jira.mariadb.org/browse/MDEV-39354"/>
-    <hyperlink ref="D28" r:id="rId27" display="https://jira.mariadb.org/browse/MDEV-39434"/>
+    <hyperlink ref="D28" r:id="rId27" display="https://jira.mariadb.org/browse/MDEV-41160" tooltip="https://jira.mariadb.org/browse/MDEV-41160"/>
     <hyperlink ref="D29" r:id="rId28" display="https://perconadev.atlassian.net/browse/PS-11042"/>
     <hyperlink ref="D30" r:id="rId29" display="https://perconadev.atlassian.net/browse/PS-11043"/>
     <hyperlink ref="D31" r:id="rId30" display="https://perconadev.atlassian.net/browse/PS-11044"/>
@@ -5278,7 +5275,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E99:E129 E95:E96 E92:E93 E88:E89 E81 E67:E79 E63 E41:E42 E30:E39 E19:E28 E3:E17" listDataValidation="1"/>
+    <ignoredError sqref="E3:E17 E19:E28 E30:E39 E41:E42 E63 E67:E79 E81 E88:E89 E92:E93 E95:E96 E99:E129" listDataValidation="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
